--- a/Windows_Ransomware_Intrusion/evidence/FileSystem/metadata/Vendors 20260424081102.xlsx
+++ b/Windows_Ransomware_Intrusion/evidence/FileSystem/metadata/Vendors 20260424081102.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emma\Desktop\evidence\FileSystem\metadata\Parsed Metadata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emma/DFIR-Simulation-Platform/Windows_Ransomware_Intrusion/evidence/FileSystem/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{369B3008-B46F-4D11-9218-07C63793DAD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D55C50F-3474-F744-8406-4DE4EA9DA5DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8508" yWindow="0" windowWidth="14628" windowHeight="12336" xr2:uid="{51604AD3-76D3-4073-BCAC-C879E96E582A}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="23120" windowHeight="12460" xr2:uid="{51604AD3-76D3-4073-BCAC-C879E96E582A}"/>
   </bookViews>
   <sheets>
     <sheet name="Vendors 20260424081102" sheetId="1" r:id="rId1"/>
@@ -636,6 +636,23 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCF7BD1-0E7B-7945-A731-5F18B651709A}" name="Table1" displayName="Table1" ref="A1:H5" totalsRowShown="0">
+  <autoFilter ref="A1:H5" xr:uid="{EFCF7BD1-0E7B-7945-A731-5F18B651709A}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{C6BC4E69-7F67-9444-8455-6258D6C66F52}" name="Name"/>
+    <tableColumn id="2" xr3:uid="{7C7FA634-4EB0-DB47-A753-85191F49DFC4}" name="Modified Time"/>
+    <tableColumn id="3" xr3:uid="{93D11FEE-5F0E-F44B-8C60-62177BD536F9}" name="Change Time"/>
+    <tableColumn id="4" xr3:uid="{082146CA-BC4B-1645-98B6-85BFA00F57A9}" name="Access Time"/>
+    <tableColumn id="5" xr3:uid="{E2D715BD-F511-D346-A6EC-80DA0A4FD611}" name="Created Time"/>
+    <tableColumn id="6" xr3:uid="{5BFD5645-84E2-814A-9E63-E7907C3107C2}" name="Size"/>
+    <tableColumn id="7" xr3:uid="{5ED65489-85CA-AD46-BB6A-81415039DFF9}" name="Location"/>
+    <tableColumn id="8" xr3:uid="{2CA2ACE6-E84C-6444-9E41-5121CE428BA3}" name="Extension"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -956,16 +973,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E8A7EF9-B648-4CB2-B6CA-146B654C1B2E}">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="59.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="21" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -991,7 +1008,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1017,7 +1034,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1043,7 +1060,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -1069,7 +1086,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -1097,5 +1114,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>